--- a/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-tiny_human_railway_animal.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-tiny_human_railway_animal.xlsx
@@ -594,53 +594,53 @@
         <v>104</v>
       </c>
       <c r="C2" t="n">
-        <v>33.62757921218872</v>
+        <v>36.45807576179504</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7699999809265137</v>
+        <v>0.8100000023841858</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0302059283623328</v>
+        <v>0.0304603691284472</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6693814992904663</v>
+        <v>0.662481427192688</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6528557538986206</v>
+        <v>0.6510761976242065</v>
       </c>
       <c r="H2" t="n">
-        <v>0.616102933883667</v>
+        <v>0.5961630344390869</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6268311142921448</v>
+        <v>0.6134405732154846</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0305113792419433</v>
+        <v>0.0304033756256103</v>
       </c>
       <c r="K2" t="n">
-        <v>17.24498081207275</v>
+        <v>17.53352737426758</v>
       </c>
       <c r="L2" t="n">
-        <v>1.183608055114746</v>
+        <v>1.125787258148193</v>
       </c>
       <c r="M2" t="n">
-        <v>3.32447361946106</v>
+        <v>3.406899929046631</v>
       </c>
       <c r="N2" t="n">
-        <v>3.914591789245605</v>
+        <v>4.042019844055176</v>
       </c>
       <c r="O2" t="n">
-        <v>0.197268009185791</v>
+        <v>0.1876312096913655</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5540789365768433</v>
+        <v>0.5678166548411051</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6524319648742676</v>
+        <v>0.6736699740091959</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-114539</t>
+          <t>20250720-043040</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -665,22 +665,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -690,10 +690,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -712,56 +712,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C3" t="n">
-        <v>35.65826535224915</v>
+        <v>36.76114797592163</v>
       </c>
       <c r="D3" t="n">
         <v>0.7699999809265137</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0302783589844309</v>
+        <v>0.0308015805024366</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6502916812896729</v>
+        <v>0.6583503484725952</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6267217397689819</v>
+        <v>0.6390154361724854</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5658854246139526</v>
+        <v>0.5856920480728149</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5762766599655151</v>
+        <v>0.5970742106437683</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0306715965270996</v>
+        <v>0.030773639678955</v>
       </c>
       <c r="K3" t="n">
-        <v>17.02845311164856</v>
+        <v>17.62287211418152</v>
       </c>
       <c r="L3" t="n">
-        <v>1.121143102645874</v>
+        <v>1.131823301315308</v>
       </c>
       <c r="M3" t="n">
-        <v>3.253628253936768</v>
+        <v>3.252345561981201</v>
       </c>
       <c r="N3" t="n">
-        <v>3.812708139419556</v>
+        <v>4.091201782226562</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1868571837743123</v>
+        <v>0.1886372168858846</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5422713756561279</v>
+        <v>0.5420575936635336</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6354513565699259</v>
+        <v>0.6818669637044271</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-114732</t>
+          <t>20250720-043232</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -786,22 +786,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -811,10 +811,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -833,56 +833,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C4" t="n">
-        <v>34.29580044746399</v>
+        <v>37.77942299842834</v>
       </c>
       <c r="D4" t="n">
         <v>0.7699999809265137</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0305001987860752</v>
+        <v>0.0308628344754559</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6646910905838013</v>
+        <v>0.6553407311439514</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6405811309814453</v>
+        <v>0.6433175206184387</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5968900322914124</v>
+        <v>0.5904541015625</v>
       </c>
       <c r="I4" t="n">
-        <v>0.613323450088501</v>
+        <v>0.6071197986602783</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0318996906280517</v>
+        <v>0.0465865135192871</v>
       </c>
       <c r="K4" t="n">
-        <v>17.06836676597595</v>
+        <v>17.45291924476624</v>
       </c>
       <c r="L4" t="n">
-        <v>1.12932014465332</v>
+        <v>1.179269313812256</v>
       </c>
       <c r="M4" t="n">
-        <v>3.357436418533325</v>
+        <v>3.370163202285767</v>
       </c>
       <c r="N4" t="n">
-        <v>3.865119695663452</v>
+        <v>4.00613260269165</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1882200241088867</v>
+        <v>0.1965448856353759</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5595727364222208</v>
+        <v>0.5616938670476278</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6441866159439087</v>
+        <v>0.667688767115275</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-114921</t>
+          <t>20250720-043423</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -907,22 +907,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -932,10 +932,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -954,56 +954,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C5" t="n">
-        <v>33.36556696891785</v>
+        <v>37.59170246124268</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7699999809265137</v>
+        <v>0.8100000023841858</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0300332903861999</v>
+        <v>0.0307358098686287</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6627746820449829</v>
+        <v>0.6582750082015991</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6416776180267334</v>
+        <v>0.6393684148788452</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6054708361625671</v>
+        <v>0.5846055746078491</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6175531148910522</v>
+        <v>0.5983153581619263</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0335047245025634</v>
+        <v>0.0281958580017089</v>
       </c>
       <c r="K5" t="n">
-        <v>17.09444761276245</v>
+        <v>17.36346197128296</v>
       </c>
       <c r="L5" t="n">
-        <v>1.143147468566894</v>
+        <v>1.164453983306885</v>
       </c>
       <c r="M5" t="n">
-        <v>3.348676919937134</v>
+        <v>3.236575603485107</v>
       </c>
       <c r="N5" t="n">
-        <v>3.733689069747925</v>
+        <v>3.91330885887146</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1905245780944824</v>
+        <v>0.1940756638844808</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5581128199895223</v>
+        <v>0.5394292672475179</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6222815116246542</v>
+        <v>0.6522181431452433</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-115108</t>
+          <t>20250720-043616</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1028,22 +1028,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1053,10 +1053,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1075,56 +1075,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C6" t="n">
-        <v>36.57511806488037</v>
+        <v>37.24337792396545</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8100000023841858</v>
+        <v>0.7699999809265137</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0303789941888106</v>
+        <v>0.0304783528004217</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6513453722000122</v>
+        <v>0.6758353710174561</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6322325468063354</v>
+        <v>0.6658546328544617</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5974817872047424</v>
+        <v>0.6186037659645081</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6156779527664185</v>
+        <v>0.6301876306533813</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0314292907714843</v>
+        <v>0.0331566333770751</v>
       </c>
       <c r="K6" t="n">
-        <v>17.06100964546204</v>
+        <v>17.36075520515442</v>
       </c>
       <c r="L6" t="n">
-        <v>1.109899044036865</v>
+        <v>1.204114198684692</v>
       </c>
       <c r="M6" t="n">
-        <v>3.132333517074585</v>
+        <v>3.208827495574951</v>
       </c>
       <c r="N6" t="n">
-        <v>3.825742721557617</v>
+        <v>4.013649225234985</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1849831740061442</v>
+        <v>0.200685699780782</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5220555861790975</v>
+        <v>0.5348045825958252</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6376237869262695</v>
+        <v>0.6689415375391642</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-115255</t>
+          <t>20250720-043808</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1174,10 +1174,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1362,56 +1362,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C2" t="n">
-        <v>50.25594544410706</v>
+        <v>54.70855712890625</v>
       </c>
       <c r="D2" t="n">
-        <v>1.940000057220459</v>
+        <v>1.879999995231628</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1547981546475337</v>
+        <v>0.1589160424853683</v>
       </c>
       <c r="F2" t="n">
-        <v>0.657784104347229</v>
+        <v>0.6471351385116577</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6525732278823853</v>
+        <v>0.6354399919509888</v>
       </c>
       <c r="H2" t="n">
-        <v>0.568135142326355</v>
+        <v>0.5758244395256042</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6035830974578857</v>
+        <v>0.5798583030700684</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0621426105499267</v>
+        <v>0.0643284320831298</v>
       </c>
       <c r="K2" t="n">
-        <v>27.39710855484009</v>
+        <v>27.1875069141388</v>
       </c>
       <c r="L2" t="n">
-        <v>1.249207258224487</v>
+        <v>1.388995409011841</v>
       </c>
       <c r="M2" t="n">
-        <v>3.762962818145752</v>
+        <v>3.897054433822632</v>
       </c>
       <c r="N2" t="n">
-        <v>5.592981815338135</v>
+        <v>5.842442512512207</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2082012097040812</v>
+        <v>0.2314992348353068</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6271604696909586</v>
+        <v>0.649509072303772</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9321636358896892</v>
+        <v>0.9737404187520344</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-114808</t>
+          <t>20250718-081243</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1436,22 +1436,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1461,10 +1461,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1483,56 +1483,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C3" t="n">
-        <v>50.36313700675965</v>
+        <v>55.02376770973206</v>
       </c>
       <c r="D3" t="n">
-        <v>1.879999995231628</v>
+        <v>1.809999942779541</v>
       </c>
       <c r="E3" t="n">
-        <v>0.153690008016733</v>
+        <v>0.1626946947990207</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6901444792747498</v>
+        <v>0.6860097050666809</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6673389673233032</v>
+        <v>0.6350861787796021</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6083611249923706</v>
+        <v>0.5735282897949219</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6179769039154053</v>
+        <v>0.5904849767684937</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0567631721496582</v>
+        <v>0.06573128700256339</v>
       </c>
       <c r="K3" t="n">
-        <v>26.28646469116211</v>
+        <v>27.18326091766357</v>
       </c>
       <c r="L3" t="n">
-        <v>1.324488401412964</v>
+        <v>1.697369813919067</v>
       </c>
       <c r="M3" t="n">
-        <v>3.771610260009766</v>
+        <v>4.266744613647461</v>
       </c>
       <c r="N3" t="n">
-        <v>5.516409158706665</v>
+        <v>5.909223318099976</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2207480669021606</v>
+        <v>0.2828949689865112</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6286017100016276</v>
+        <v>0.7111241022745768</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9194015264511108</v>
+        <v>0.9848705530166626</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-115045</t>
+          <t>20250718-081521</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1557,22 +1557,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1582,10 +1582,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1607,53 +1607,53 @@
         <v>119</v>
       </c>
       <c r="C4" t="n">
-        <v>57.13878011703491</v>
+        <v>59.45315217971802</v>
       </c>
       <c r="D4" t="n">
-        <v>1.879999995231628</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1545143848707696</v>
+        <v>0.1581056839277764</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6666104793548584</v>
+        <v>0.7022587656974792</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6063495278358459</v>
+        <v>0.6771821975708008</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5673500895500183</v>
+        <v>0.6161133050918579</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5570778846740723</v>
+        <v>0.6249626874923706</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06927108764648431</v>
+        <v>0.0636425018310546</v>
       </c>
       <c r="K4" t="n">
-        <v>26.88014221191406</v>
+        <v>27.01202297210693</v>
       </c>
       <c r="L4" t="n">
-        <v>1.634610891342163</v>
+        <v>1.421429395675659</v>
       </c>
       <c r="M4" t="n">
-        <v>4.0330810546875</v>
+        <v>3.933868885040283</v>
       </c>
       <c r="N4" t="n">
-        <v>6.004221677780151</v>
+        <v>5.932942390441895</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2724351485570271</v>
+        <v>0.2369048992792765</v>
       </c>
       <c r="P4" t="n">
-        <v>0.67218017578125</v>
+        <v>0.6556448141733805</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.000703612963359</v>
+        <v>0.9888237317403158</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-115315</t>
+          <t>20250718-081759</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1678,22 +1678,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1703,10 +1703,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1728,53 +1728,53 @@
         <v>104</v>
       </c>
       <c r="C5" t="n">
-        <v>50.14104986190796</v>
+        <v>52.22027373313904</v>
       </c>
       <c r="D5" t="n">
         <v>1.809999942779541</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1562319718874417</v>
+        <v>0.1581030946511488</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6779874563217163</v>
+        <v>0.6784218549728394</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6825991868972778</v>
+        <v>0.6526472568511963</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6153044700622559</v>
+        <v>0.5813831686973572</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6156937479972839</v>
+        <v>0.5865321755409241</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0587198734283447</v>
+        <v>0.06695199012756339</v>
       </c>
       <c r="K5" t="n">
-        <v>26.36479163169861</v>
+        <v>27.44209146499633</v>
       </c>
       <c r="L5" t="n">
-        <v>1.611321210861206</v>
+        <v>1.717432260513306</v>
       </c>
       <c r="M5" t="n">
-        <v>3.997910261154175</v>
+        <v>3.863162755966187</v>
       </c>
       <c r="N5" t="n">
-        <v>6.096197843551636</v>
+        <v>5.975803136825562</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2685535351435343</v>
+        <v>0.2862387100855509</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6663183768590292</v>
+        <v>0.6438604593276978</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.016032973925273</v>
+        <v>0.9959671894709268</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-115552</t>
+          <t>20250718-082040</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1799,22 +1799,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1824,10 +1824,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1849,53 +1849,53 @@
         <v>109</v>
       </c>
       <c r="C6" t="n">
-        <v>52.22058939933777</v>
+        <v>53.0766978263855</v>
       </c>
       <c r="D6" t="n">
-        <v>1.940000057220459</v>
+        <v>1.879999995231628</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1529844857137137</v>
+        <v>0.154566865448558</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6650513410568237</v>
+        <v>0.6390262246131897</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6640886664390564</v>
+        <v>0.614453911781311</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5986157059669495</v>
+        <v>0.5698897838592529</v>
       </c>
       <c r="I6" t="n">
-        <v>0.620527982711792</v>
+        <v>0.5648249387741089</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0619919300079345</v>
+        <v>0.07105851173400871</v>
       </c>
       <c r="K6" t="n">
-        <v>20.71722555160522</v>
+        <v>27.47228503227234</v>
       </c>
       <c r="L6" t="n">
-        <v>1.317600727081299</v>
+        <v>1.435880899429321</v>
       </c>
       <c r="M6" t="n">
-        <v>3.772907018661499</v>
+        <v>3.947920322418213</v>
       </c>
       <c r="N6" t="n">
-        <v>5.571422338485718</v>
+        <v>5.896742820739746</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2196001211802164</v>
+        <v>0.2393134832382202</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6288178364435831</v>
+        <v>0.6579867204030355</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9285703897476196</v>
+        <v>0.982790470123291</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-115821</t>
+          <t>20250718-082315</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1945,10 +1945,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2133,56 +2133,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C2" t="n">
-        <v>49.54992365837097</v>
+        <v>49.91915106773376</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9300000071525574</v>
+        <v>0.8199999928474426</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1247605335812608</v>
+        <v>0.1306037129017344</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5240976214408875</v>
+        <v>0.559049129486084</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5141736268997192</v>
+        <v>0.5527282953262329</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4526654481887817</v>
+        <v>0.4697427153587341</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4220412969589233</v>
+        <v>0.3952880799770355</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0517878532409668</v>
+        <v>0.0636677742004394</v>
       </c>
       <c r="K2" t="n">
-        <v>23.68334817886353</v>
+        <v>23.90707659721375</v>
       </c>
       <c r="L2" t="n">
-        <v>1.458652257919312</v>
+        <v>1.508503913879394</v>
       </c>
       <c r="M2" t="n">
-        <v>4.770106315612793</v>
+        <v>4.865602731704712</v>
       </c>
       <c r="N2" t="n">
-        <v>7.777949810028076</v>
+        <v>8.234938383102417</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2431087096532186</v>
+        <v>0.2514173189798991</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7950177192687988</v>
+        <v>0.810933788617452</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.296324968338013</v>
+        <v>1.37248973051707</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-145344</t>
+          <t>20250718-142200</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2207,22 +2207,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -2232,10 +2232,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2254,56 +2254,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C3" t="n">
-        <v>44.22089982032776</v>
+        <v>51.65755534172058</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.9300000071525574</v>
       </c>
       <c r="E3" t="n">
-        <v>0.122809737920761</v>
+        <v>0.1310891143414152</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5170691013336182</v>
+        <v>0.5459414124488831</v>
       </c>
       <c r="G3" t="n">
-        <v>0.563745379447937</v>
+        <v>0.5362982749938965</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4962502121925354</v>
+        <v>0.4551478028297424</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3081337213516235</v>
+        <v>0.3675386011600494</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0542695522308349</v>
+        <v>0.0529663562774658</v>
       </c>
       <c r="K3" t="n">
-        <v>23.63849425315857</v>
+        <v>24.03808355331421</v>
       </c>
       <c r="L3" t="n">
-        <v>1.192955493927002</v>
+        <v>1.209650993347168</v>
       </c>
       <c r="M3" t="n">
-        <v>4.734049081802368</v>
+        <v>4.883680820465088</v>
       </c>
       <c r="N3" t="n">
-        <v>7.893173694610596</v>
+        <v>8.329090118408203</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1988259156545003</v>
+        <v>0.2016084988911946</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7890081803003947</v>
+        <v>0.813946803410848</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.315528949101766</v>
+        <v>1.388181686401367</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-145618</t>
+          <t>20250718-142431</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -2328,22 +2328,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -2353,10 +2353,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2375,56 +2375,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C4" t="n">
-        <v>43.71048259735107</v>
+        <v>48.58184170722961</v>
       </c>
       <c r="D4" t="n">
         <v>0.8700000047683716</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1227276050127469</v>
+        <v>0.1327024818560398</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5387274026870728</v>
+        <v>0.5467156171798706</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5246990323066711</v>
+        <v>0.5277916193008423</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4901050329208374</v>
+        <v>0.4404500424861908</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4719690978527069</v>
+        <v>0.3918160200119018</v>
       </c>
       <c r="J4" t="n">
-        <v>0.051053762435913</v>
+        <v>0.0454730987548828</v>
       </c>
       <c r="K4" t="n">
-        <v>23.77972602844238</v>
+        <v>24.26550436019897</v>
       </c>
       <c r="L4" t="n">
-        <v>1.422501087188721</v>
+        <v>1.171926259994507</v>
       </c>
       <c r="M4" t="n">
-        <v>4.73430323600769</v>
+        <v>5.20591926574707</v>
       </c>
       <c r="N4" t="n">
-        <v>7.874764442443848</v>
+        <v>8.412823438644409</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2370835145314534</v>
+        <v>0.1953210433324178</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7890505393346151</v>
+        <v>0.8676532109578451</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.312460740407308</v>
+        <v>1.402137239774068</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-145841</t>
+          <t>20250718-142704</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -2474,10 +2474,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2496,56 +2496,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C5" t="n">
-        <v>45.12030053138733</v>
+        <v>50.35176086425781</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.9300000071525574</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1278211176395416</v>
+        <v>0.1304332373435036</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5584053993225098</v>
+        <v>0.6653591394424438</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5460628271102905</v>
+        <v>0.6573480367660522</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4717552363872528</v>
+        <v>0.5877595543861389</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4000140428543091</v>
+        <v>0.4144032597541809</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0635747909545898</v>
+        <v>0.0466084480285644</v>
       </c>
       <c r="K5" t="n">
-        <v>23.72634434700012</v>
+        <v>24.28187608718872</v>
       </c>
       <c r="L5" t="n">
-        <v>1.463994979858398</v>
+        <v>1.211792469024658</v>
       </c>
       <c r="M5" t="n">
-        <v>4.619738817214966</v>
+        <v>5.161906957626343</v>
       </c>
       <c r="N5" t="n">
-        <v>7.750829935073853</v>
+        <v>8.306535720825195</v>
       </c>
       <c r="O5" t="n">
-        <v>0.243999163309733</v>
+        <v>0.2019654115041097</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7699564695358276</v>
+        <v>0.8603178262710571</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.291804989178975</v>
+        <v>1.384422620137532</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-150103</t>
+          <t>20250718-142933</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2570,22 +2570,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2595,10 +2595,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2620,53 +2620,53 @@
         <v>109</v>
       </c>
       <c r="C6" t="n">
-        <v>45.75303387641907</v>
+        <v>48.48200058937073</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8700000047683716</v>
+        <v>0.8199999928474426</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1257106667264885</v>
+        <v>0.1324840707516451</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5187005400657654</v>
+        <v>0.5390551090240479</v>
       </c>
       <c r="G6" t="n">
-        <v>0.513282299041748</v>
+        <v>0.5356808304786682</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4383150041103363</v>
+        <v>0.4793267548084259</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3485797941684723</v>
+        <v>0.4114625155925751</v>
       </c>
       <c r="J6" t="n">
-        <v>0.052886962890625</v>
+        <v>0.0632970333099365</v>
       </c>
       <c r="K6" t="n">
-        <v>23.67052507400513</v>
+        <v>24.14178419113159</v>
       </c>
       <c r="L6" t="n">
-        <v>1.468072891235352</v>
+        <v>1.506988286972046</v>
       </c>
       <c r="M6" t="n">
-        <v>4.693963527679443</v>
+        <v>4.808172225952148</v>
       </c>
       <c r="N6" t="n">
-        <v>7.748290300369263</v>
+        <v>8.24954628944397</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2446788152058919</v>
+        <v>0.251164714495341</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7823272546132406</v>
+        <v>0.8013620376586914</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.29138171672821</v>
+        <v>1.374924381573995</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-150326</t>
+          <t>20250718-143205</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2691,22 +2691,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2716,10 +2716,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2907,53 +2907,53 @@
         <v>114</v>
       </c>
       <c r="C2" t="n">
-        <v>77.52689146995544</v>
+        <v>79.4699764251709</v>
       </c>
       <c r="D2" t="n">
-        <v>6.480000019073486</v>
+        <v>6.440000057220459</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2878236059556928</v>
+        <v>0.2948786417643229</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5691262483596802</v>
+        <v>0.614651083946228</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5579482316970825</v>
+        <v>0.5833204388618469</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4960413575172424</v>
+        <v>0.4926593899726867</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0913326144218444</v>
+        <v>0.3052634298801422</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1031005382537841</v>
+        <v>0.09826493263244621</v>
       </c>
       <c r="K2" t="n">
-        <v>78.14948463439941</v>
+        <v>80.53887820243835</v>
       </c>
       <c r="L2" t="n">
-        <v>2.008408069610596</v>
+        <v>1.958956956863404</v>
       </c>
       <c r="M2" t="n">
-        <v>6.458173036575317</v>
+        <v>6.586667060852051</v>
       </c>
       <c r="N2" t="n">
-        <v>13.4130802154541</v>
+        <v>14.06648659706116</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3347346782684326</v>
+        <v>0.3264928261439005</v>
       </c>
       <c r="P2" t="n">
-        <v>1.076362172762553</v>
+        <v>1.097777843475342</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.23551336924235</v>
+        <v>2.344414432843526</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-174524</t>
+          <t>20250718-195910</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2978,22 +2978,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3003,10 +3003,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3025,56 +3025,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C3" t="n">
-        <v>71.45166230201721</v>
+        <v>77.62743735313416</v>
       </c>
       <c r="D3" t="n">
-        <v>6.480000019073486</v>
+        <v>6.440000057220459</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2906253727582785</v>
+        <v>0.2982016790897474</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5489224791526794</v>
+        <v>0.6392878890037537</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5498459339141846</v>
+        <v>0.6243941783905029</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4703123271465301</v>
+        <v>0.5610353946685791</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3311218917369842</v>
+        <v>0.3256377875804901</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1018412113189697</v>
+        <v>0.1083700656890869</v>
       </c>
       <c r="K3" t="n">
-        <v>72.35891079902649</v>
+        <v>80.823734998703</v>
       </c>
       <c r="L3" t="n">
-        <v>2.237915754318237</v>
+        <v>2.369732856750488</v>
       </c>
       <c r="M3" t="n">
-        <v>6.183515310287476</v>
+        <v>6.607530355453491</v>
       </c>
       <c r="N3" t="n">
-        <v>13.373295545578</v>
+        <v>14.1459481716156</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3729859590530395</v>
+        <v>0.3949554761250813</v>
       </c>
       <c r="P3" t="n">
-        <v>1.030585885047913</v>
+        <v>1.101255059242248</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.228882590929667</v>
+        <v>2.3576580286026</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-174958</t>
+          <t>20250718-200345</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3099,22 +3099,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3124,10 +3124,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3149,53 +3149,53 @@
         <v>104</v>
       </c>
       <c r="C4" t="n">
-        <v>72.78758859634399</v>
+        <v>71.32682132720947</v>
       </c>
       <c r="D4" t="n">
         <v>6.440000057220459</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2927641983215625</v>
+        <v>0.2987134892206926</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5212838649749756</v>
+        <v>0.6171367764472961</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5081971883773804</v>
+        <v>0.5992616415023804</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4304528832435608</v>
+        <v>0.5191515684127808</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3118726909160614</v>
+        <v>0.3346635103225708</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1006777286529541</v>
+        <v>0.1014385223388671</v>
       </c>
       <c r="K4" t="n">
-        <v>78.49455499649048</v>
+        <v>74.65886282920837</v>
       </c>
       <c r="L4" t="n">
-        <v>1.93695592880249</v>
+        <v>2.27964973449707</v>
       </c>
       <c r="M4" t="n">
-        <v>6.459430932998657</v>
+        <v>6.808593034744263</v>
       </c>
       <c r="N4" t="n">
-        <v>13.61637020111084</v>
+        <v>14.10869860649109</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3228259881337483</v>
+        <v>0.3799416224161784</v>
       </c>
       <c r="P4" t="n">
-        <v>1.076571822166443</v>
+        <v>1.13476550579071</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.269395033518473</v>
+        <v>2.351449767748515</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-175418</t>
+          <t>20250718-200817</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3220,22 +3220,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -3245,10 +3245,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3267,56 +3267,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C5" t="n">
-        <v>71.52859926223755</v>
+        <v>81.91268277168274</v>
       </c>
       <c r="D5" t="n">
         <v>6.480000019073486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2890176131175114</v>
+        <v>0.2992372721956487</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6627640724182129</v>
+        <v>0.6301993131637573</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6125032901763916</v>
+        <v>0.5995290279388428</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5658372044563293</v>
+        <v>0.5269789099693298</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2951617240905761</v>
+        <v>0.3343516886234283</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1020905971527099</v>
+        <v>0.1065397262573242</v>
       </c>
       <c r="K5" t="n">
-        <v>72.12388682365417</v>
+        <v>81.08261108398438</v>
       </c>
       <c r="L5" t="n">
-        <v>2.236596345901489</v>
+        <v>2.009196043014526</v>
       </c>
       <c r="M5" t="n">
-        <v>6.183204650878906</v>
+        <v>6.6134934425354</v>
       </c>
       <c r="N5" t="n">
-        <v>13.48139357566834</v>
+        <v>14.22904300689697</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3727660576502482</v>
+        <v>0.3348660071690877</v>
       </c>
       <c r="P5" t="n">
-        <v>1.030534108479818</v>
+        <v>1.102248907089233</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.246898929278056</v>
+        <v>2.371507167816162</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-175840</t>
+          <t>20250718-201238</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3341,22 +3341,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -3366,10 +3366,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3388,56 +3388,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C6" t="n">
-        <v>70.76572942733765</v>
+        <v>74.99464440345764</v>
       </c>
       <c r="D6" t="n">
         <v>6.480000019073486</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2892740231293898</v>
+        <v>0.2961866221296678</v>
       </c>
       <c r="F6" t="n">
-        <v>0.611015260219574</v>
+        <v>0.6213536262512207</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5830930471420288</v>
+        <v>0.599226176738739</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4955174028873443</v>
+        <v>0.5230228304862976</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3145782053470611</v>
+        <v>0.3286988735198974</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1122303009033203</v>
+        <v>0.1051743030548095</v>
       </c>
       <c r="K6" t="n">
-        <v>71.96509647369385</v>
+        <v>81.32683682441711</v>
       </c>
       <c r="L6" t="n">
-        <v>2.30793285369873</v>
+        <v>2.010254859924316</v>
       </c>
       <c r="M6" t="n">
-        <v>6.104448080062866</v>
+        <v>6.614840269088745</v>
       </c>
       <c r="N6" t="n">
-        <v>13.89456510543823</v>
+        <v>14.55279970169067</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3846554756164551</v>
+        <v>0.3350424766540527</v>
       </c>
       <c r="P6" t="n">
-        <v>1.017408013343811</v>
+        <v>1.102473378181458</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.315760850906372</v>
+        <v>2.425466616948446</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-180300</t>
+          <t>20250718-201715</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3462,22 +3462,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3487,10 +3487,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3675,56 +3675,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="C2" t="n">
-        <v>71.46007084846497</v>
+        <v>97.84995794296265</v>
       </c>
       <c r="D2" t="n">
         <v>5.739999771118164</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1646957466235527</v>
+        <v>0.1658405279941695</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4155859053134918</v>
+        <v>0.5834954977035522</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4157537817955017</v>
+        <v>0.5879294276237488</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4192255437374115</v>
+        <v>0.5622175931930542</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4167906641960144</v>
+        <v>0.5137215256690979</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0665938854217529</v>
+        <v>0.065936803817749</v>
       </c>
       <c r="K2" t="n">
-        <v>28.51053524017334</v>
+        <v>28.7547128200531</v>
       </c>
       <c r="L2" t="n">
-        <v>1.684403896331787</v>
+        <v>2.06320333480835</v>
       </c>
       <c r="M2" t="n">
-        <v>3.966160774230957</v>
+        <v>4.048621416091919</v>
       </c>
       <c r="N2" t="n">
-        <v>6.97020411491394</v>
+        <v>7.19835352897644</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2807339827219645</v>
+        <v>0.3438672224680583</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6610267957051595</v>
+        <v>0.6747702360153198</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.16170068581899</v>
+        <v>1.19972558816274</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-043016</t>
+          <t>20250719-125136</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3749,22 +3749,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3774,10 +3774,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3799,53 +3799,53 @@
         <v>104</v>
       </c>
       <c r="C3" t="n">
-        <v>72.54845666885376</v>
+        <v>73.97748851776123</v>
       </c>
       <c r="D3" t="n">
-        <v>5.739999771118164</v>
+        <v>5.730000019073486</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1634754102963667</v>
+        <v>0.1649855352365053</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4172146320343017</v>
+        <v>0.413469910621643</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4131297767162323</v>
+        <v>0.4130900800228119</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4039971232414245</v>
+        <v>0.4124080538749695</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4040884375572204</v>
+        <v>0.4035665094852447</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0635280609130859</v>
+        <v>0.0664279460906982</v>
       </c>
       <c r="K3" t="n">
-        <v>22.05990529060364</v>
+        <v>23.06320762634277</v>
       </c>
       <c r="L3" t="n">
-        <v>1.709735155105591</v>
+        <v>1.776934862136841</v>
       </c>
       <c r="M3" t="n">
-        <v>3.845471620559693</v>
+        <v>3.957690715789795</v>
       </c>
       <c r="N3" t="n">
-        <v>6.609029054641724</v>
+        <v>6.854444980621338</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2849558591842651</v>
+        <v>0.2961558103561401</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6409119367599487</v>
+        <v>0.6596151192982992</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.101504842440287</v>
+        <v>1.142407496770223</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-043308</t>
+          <t>20250719-125456</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3870,22 +3870,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3895,10 +3895,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3917,56 +3917,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C4" t="n">
-        <v>78.79887270927429</v>
+        <v>81.5395143032074</v>
       </c>
       <c r="D4" t="n">
         <v>5.730000019073486</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1656185472220705</v>
+        <v>0.1642913237339308</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4175508916378021</v>
+        <v>0.4802051782608032</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4116480350494385</v>
+        <v>0.4781227111816406</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3976601064205169</v>
+        <v>0.4612117111682892</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3344215154647827</v>
+        <v>0.4560591578483581</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0659718513488769</v>
+        <v>0.0637576580047607</v>
       </c>
       <c r="K4" t="n">
-        <v>22.4279465675354</v>
+        <v>23.13473129272461</v>
       </c>
       <c r="L4" t="n">
-        <v>1.697218418121338</v>
+        <v>1.741113662719727</v>
       </c>
       <c r="M4" t="n">
-        <v>3.920632839202881</v>
+        <v>3.949750661849976</v>
       </c>
       <c r="N4" t="n">
-        <v>6.624844074249268</v>
+        <v>6.823941230773926</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2828697363535563</v>
+        <v>0.2901856104532878</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6534388065338135</v>
+        <v>0.658291776974996</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.104140679041545</v>
+        <v>1.137323538462321</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-043600</t>
+          <t>20250719-125752</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3991,22 +3991,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4016,10 +4016,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4038,56 +4038,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C5" t="n">
-        <v>72.05029964447021</v>
+        <v>73.67531204223633</v>
       </c>
       <c r="D5" t="n">
-        <v>5.670000076293945</v>
+        <v>5.730000019073486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1642975509166717</v>
+        <v>0.1652178654976941</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4253098368644714</v>
+        <v>0.4768457412719726</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4211817681789398</v>
+        <v>0.4723275601863861</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4114455580711365</v>
+        <v>0.4424610137939453</v>
       </c>
       <c r="I5" t="n">
-        <v>0.388846218585968</v>
+        <v>0.3765975832939148</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0668914318084716</v>
+        <v>0.06755566596984861</v>
       </c>
       <c r="K5" t="n">
-        <v>22.22920608520508</v>
+        <v>28.76229119300842</v>
       </c>
       <c r="L5" t="n">
-        <v>1.709487915039062</v>
+        <v>2.053828001022339</v>
       </c>
       <c r="M5" t="n">
-        <v>3.838962316513062</v>
+        <v>3.891594648361206</v>
       </c>
       <c r="N5" t="n">
-        <v>6.503919363021851</v>
+        <v>6.880436897277832</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2849146525065104</v>
+        <v>0.3423046668370564</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6398270527521769</v>
+        <v>0.648599108060201</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.083986560503642</v>
+        <v>1.146739482879639</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-043858</t>
+          <t>20250719-130055</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4112,22 +4112,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4137,10 +4137,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4159,56 +4159,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="C6" t="n">
-        <v>69.10601568222046</v>
+        <v>104.6239199638367</v>
       </c>
       <c r="D6" t="n">
         <v>5.730000019073486</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1636093235932863</v>
+        <v>0.1670928193418771</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4582656025886535</v>
+        <v>0.5347345471382141</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4583975970745086</v>
+        <v>0.5295642018318176</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4596216976642608</v>
+        <v>0.4964151382446289</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4553302228450775</v>
+        <v>0.4713392853736877</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0667917728424072</v>
+        <v>0.06496262550354</v>
       </c>
       <c r="K6" t="n">
-        <v>27.68836808204651</v>
+        <v>22.75575304031372</v>
       </c>
       <c r="L6" t="n">
-        <v>1.701778888702393</v>
+        <v>1.789566278457642</v>
       </c>
       <c r="M6" t="n">
-        <v>3.868121147155762</v>
+        <v>4.040817260742188</v>
       </c>
       <c r="N6" t="n">
-        <v>6.626180410385132</v>
+        <v>6.809996366500855</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2836298147837321</v>
+        <v>0.2982610464096069</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6446868578592936</v>
+        <v>0.6734695434570312</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.104363401730855</v>
+        <v>1.134999394416809</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-044149</t>
+          <t>20250719-130351</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4233,22 +4233,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4258,10 +4258,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4446,56 +4446,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="C2" t="n">
-        <v>49.98662829399109</v>
+        <v>62.70809245109558</v>
       </c>
       <c r="D2" t="n">
-        <v>3.359999895095825</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1030742903368188</v>
+        <v>0.1048330683862009</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4197922348976135</v>
+        <v>0.4830430150032043</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4185283780097961</v>
+        <v>0.4818252325057983</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4167751967906952</v>
+        <v>0.4656838476657867</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4104275107383728</v>
+        <v>0.4534772336483001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0428926944732666</v>
+        <v>0.0423731803894043</v>
       </c>
       <c r="K2" t="n">
-        <v>18.11421942710876</v>
+        <v>18.28100419044494</v>
       </c>
       <c r="L2" t="n">
-        <v>1.19028377532959</v>
+        <v>1.24070143699646</v>
       </c>
       <c r="M2" t="n">
-        <v>3.117843866348267</v>
+        <v>2.963818073272705</v>
       </c>
       <c r="N2" t="n">
-        <v>4.167340993881226</v>
+        <v>4.363518238067627</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1983806292215983</v>
+        <v>0.2067835728327433</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5196406443913778</v>
+        <v>0.4939696788787842</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6945568323135376</v>
+        <v>0.7272530396779379</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-073604</t>
+          <t>20250719-192628</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4520,22 +4520,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4545,10 +4545,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4567,56 +4567,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C3" t="n">
-        <v>47.57813596725464</v>
+        <v>59.37469696998596</v>
       </c>
       <c r="D3" t="n">
-        <v>3.369999885559082</v>
+        <v>3.319999933242798</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1036809063874757</v>
+        <v>0.1043752862625762</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4983187019824981</v>
+        <v>0.4798779785633087</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4989188909530639</v>
+        <v>0.4810023009777069</v>
       </c>
       <c r="H3" t="n">
-        <v>0.478103905916214</v>
+        <v>0.4688295423984527</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4502460658550262</v>
+        <v>0.431626558303833</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0399298667907714</v>
+        <v>0.041750431060791</v>
       </c>
       <c r="K3" t="n">
-        <v>18.04218435287476</v>
+        <v>18.5976037979126</v>
       </c>
       <c r="L3" t="n">
-        <v>1.162277221679688</v>
+        <v>1.209543943405151</v>
       </c>
       <c r="M3" t="n">
-        <v>3.090232849121094</v>
+        <v>3.271190881729126</v>
       </c>
       <c r="N3" t="n">
-        <v>4.111035346984863</v>
+        <v>4.444772481918335</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1937128702799479</v>
+        <v>0.2015906572341919</v>
       </c>
       <c r="P3" t="n">
-        <v>0.515038808186849</v>
+        <v>0.5451984802881876</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6851725578308105</v>
+        <v>0.7407954136530558</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-073810</t>
+          <t>20250719-192849</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4666,10 +4666,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4688,56 +4688,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C4" t="n">
-        <v>48.4092915058136</v>
+        <v>58.50276589393616</v>
       </c>
       <c r="D4" t="n">
-        <v>3.440000057220459</v>
+        <v>3.339999914169312</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1013290619631425</v>
+        <v>0.1045664318469391</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5179361701011658</v>
+        <v>0.5468660593032837</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5178130865097046</v>
+        <v>0.5472531914710999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4859406650066376</v>
+        <v>0.518307626247406</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4681931734085083</v>
+        <v>0.4953703582286834</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0424792766571044</v>
+        <v>0.0428197383880615</v>
       </c>
       <c r="K4" t="n">
-        <v>18.01691961288452</v>
+        <v>18.13897347450256</v>
       </c>
       <c r="L4" t="n">
-        <v>1.162141084671021</v>
+        <v>1.277062654495239</v>
       </c>
       <c r="M4" t="n">
-        <v>2.785652875900269</v>
+        <v>2.951371431350708</v>
       </c>
       <c r="N4" t="n">
-        <v>4.183170080184937</v>
+        <v>4.376526832580566</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1936901807785034</v>
+        <v>0.2128437757492065</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4642754793167114</v>
+        <v>0.4918952385584513</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6971950133641561</v>
+        <v>0.7294211387634277</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-074014</t>
+          <t>20250719-193107</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4762,22 +4762,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4787,10 +4787,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4809,56 +4809,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C5" t="n">
-        <v>46.7786009311676</v>
+        <v>53.0546019077301</v>
       </c>
       <c r="D5" t="n">
-        <v>3.339999914169312</v>
+        <v>3.400000095367432</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1012816452063046</v>
+        <v>0.104106618723738</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4226033985614776</v>
+        <v>0.4218621551990509</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4233401119709015</v>
+        <v>0.4191117882728576</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4232556521892547</v>
+        <v>0.4090718030929565</v>
       </c>
       <c r="I5" t="n">
-        <v>0.415658175945282</v>
+        <v>0.3954173922538757</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0502436161041259</v>
+        <v>0.0511913299560546</v>
       </c>
       <c r="K5" t="n">
-        <v>12.48079013824463</v>
+        <v>18.45261263847351</v>
       </c>
       <c r="L5" t="n">
-        <v>1.187571048736572</v>
+        <v>1.228314876556396</v>
       </c>
       <c r="M5" t="n">
-        <v>2.788320064544678</v>
+        <v>2.931522607803345</v>
       </c>
       <c r="N5" t="n">
-        <v>4.22262716293335</v>
+        <v>4.364612340927124</v>
       </c>
       <c r="O5" t="n">
-        <v>0.197928508122762</v>
+        <v>0.2047191460927327</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4647200107574463</v>
+        <v>0.4885871013005574</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.703771193822225</v>
+        <v>0.7274353901545206</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-074219</t>
+          <t>20250719-193324</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4908,10 +4908,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4930,56 +4930,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="C6" t="n">
-        <v>45.22594094276428</v>
+        <v>75.38698315620422</v>
       </c>
       <c r="D6" t="n">
-        <v>3.400000095367432</v>
+        <v>3.369999885559082</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1036415558594923</v>
+        <v>0.1066695699444064</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4443616867065429</v>
+        <v>0.5707952976226807</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4424976408481598</v>
+        <v>0.5695808529853821</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4075694680213928</v>
+        <v>0.5357460379600525</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3871946930885315</v>
+        <v>0.5014727711677551</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0437211990356445</v>
+        <v>0.0434422492980957</v>
       </c>
       <c r="K6" t="n">
-        <v>17.99752283096313</v>
+        <v>18.16665744781494</v>
       </c>
       <c r="L6" t="n">
-        <v>1.145694017410278</v>
+        <v>1.231808185577393</v>
       </c>
       <c r="M6" t="n">
-        <v>3.12119460105896</v>
+        <v>2.833969116210937</v>
       </c>
       <c r="N6" t="n">
-        <v>4.204182147979736</v>
+        <v>4.379346370697021</v>
       </c>
       <c r="O6" t="n">
-        <v>0.190949002901713</v>
+        <v>0.2053013642628987</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5201991001764933</v>
+        <v>0.4723281860351562</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7006970246632894</v>
+        <v>0.7298910617828369</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-074422</t>
+          <t>20250719-193536</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5004,22 +5004,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5029,10 +5029,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5217,56 +5217,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C2" t="n">
-        <v>42.11831331253052</v>
+        <v>43.50282907485962</v>
       </c>
       <c r="D2" t="n">
-        <v>2.220000028610229</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1039975744027357</v>
+        <v>0.1045918486533908</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4123256802558899</v>
+        <v>0.3799217641353607</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4087785482406616</v>
+        <v>0.3800491988658905</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3988515138626098</v>
+        <v>0.3266389667987823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3530130386352539</v>
+        <v>0.3315319120883941</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0342895984649658</v>
+        <v>0.0331640243530273</v>
       </c>
       <c r="K2" t="n">
-        <v>17.44274520874023</v>
+        <v>17.83287024497986</v>
       </c>
       <c r="L2" t="n">
-        <v>1.021967649459839</v>
+        <v>1.095563888549805</v>
       </c>
       <c r="M2" t="n">
-        <v>3.000943660736084</v>
+        <v>3.093571186065674</v>
       </c>
       <c r="N2" t="n">
-        <v>4.511361598968506</v>
+        <v>4.603387594223023</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1703279415766398</v>
+        <v>0.1825939814249674</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5001572767893473</v>
+        <v>0.5155951976776123</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7518935998280843</v>
+        <v>0.767231265703837</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-094724</t>
+          <t>20250719-235026</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5291,22 +5291,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5316,10 +5316,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5338,56 +5338,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>174</v>
       </c>
       <c r="C3" t="n">
-        <v>42.89070272445679</v>
+        <v>71.29575109481812</v>
       </c>
       <c r="D3" t="n">
-        <v>2.259999990463257</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1050572716272793</v>
+        <v>0.1048318161361518</v>
       </c>
       <c r="F3" t="n">
-        <v>0.416461706161499</v>
+        <v>0.6226320266723633</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4085713028907776</v>
+        <v>0.6399800777435303</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3724043071269989</v>
+        <v>0.5787913799285889</v>
       </c>
       <c r="I3" t="n">
-        <v>0.364030659198761</v>
+        <v>0.5305467247962952</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0348434448242187</v>
+        <v>0.0406956672668457</v>
       </c>
       <c r="K3" t="n">
-        <v>17.93293833732605</v>
+        <v>17.52231693267822</v>
       </c>
       <c r="L3" t="n">
-        <v>1.034355401992798</v>
+        <v>1.09441089630127</v>
       </c>
       <c r="M3" t="n">
-        <v>2.906869411468506</v>
+        <v>2.969051361083984</v>
       </c>
       <c r="N3" t="n">
-        <v>4.418683052062988</v>
+        <v>5.106841325759888</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1723925669987996</v>
+        <v>0.1824018160502115</v>
       </c>
       <c r="P3" t="n">
-        <v>0.484478235244751</v>
+        <v>0.4948418935139974</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7364471753438314</v>
+        <v>0.8511402209599813</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-094923</t>
+          <t>20250719-235229</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5412,22 +5412,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5437,10 +5437,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5459,56 +5459,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C4" t="n">
-        <v>46.22048187255859</v>
+        <v>45.5185878276825</v>
       </c>
       <c r="D4" t="n">
         <v>2.220000028610229</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1054913830338862</v>
+        <v>0.103965866456338</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4133509397506714</v>
+        <v>0.4215139150619507</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4124817252159118</v>
+        <v>0.4159503281116485</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3884924352169037</v>
+        <v>0.3870499730110168</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3803346753120422</v>
+        <v>0.3849406838417053</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0395307540893554</v>
+        <v>0.0347070693969726</v>
       </c>
       <c r="K4" t="n">
-        <v>17.59372758865356</v>
+        <v>18.15665459632873</v>
       </c>
       <c r="L4" t="n">
-        <v>1.064446449279785</v>
+        <v>1.061548709869385</v>
       </c>
       <c r="M4" t="n">
-        <v>2.866359233856201</v>
+        <v>3.121005535125732</v>
       </c>
       <c r="N4" t="n">
-        <v>4.867347002029419</v>
+        <v>4.591790437698364</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1774077415466308</v>
+        <v>0.1769247849782308</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4777265389760335</v>
+        <v>0.5201675891876221</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8112245003382365</v>
+        <v>0.7652984062830607</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-095123</t>
+          <t>20250719-235459</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5533,22 +5533,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5558,10 +5558,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5580,56 +5580,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C5" t="n">
-        <v>43.46435022354126</v>
+        <v>42.45916223526001</v>
       </c>
       <c r="D5" t="n">
-        <v>2.230000019073486</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1016328794146896</v>
+        <v>0.1040699917536515</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4178856611251831</v>
+        <v>0.4236725568771362</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4107407331466675</v>
+        <v>0.4171542525291443</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3661502599716186</v>
+        <v>0.384510338306427</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3685799837112427</v>
+        <v>0.3749683499336242</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0413582324981689</v>
+        <v>0.0394613742828369</v>
       </c>
       <c r="K5" t="n">
-        <v>17.59100461006165</v>
+        <v>18.01372599601746</v>
       </c>
       <c r="L5" t="n">
-        <v>1.037911415100098</v>
+        <v>1.076439142227173</v>
       </c>
       <c r="M5" t="n">
-        <v>2.924684524536133</v>
+        <v>3.017840623855591</v>
       </c>
       <c r="N5" t="n">
-        <v>4.496616125106812</v>
+        <v>4.959316730499268</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1729852358500162</v>
+        <v>0.1794065237045288</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4874474207560221</v>
+        <v>0.5029734373092651</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7494360208511353</v>
+        <v>0.8265527884165446</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-095327</t>
+          <t>20250719-235704</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5679,10 +5679,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5701,56 +5701,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C6" t="n">
-        <v>42.03904867172241</v>
+        <v>48.45416378974915</v>
       </c>
       <c r="D6" t="n">
-        <v>2.259999990463257</v>
+        <v>2.319999933242798</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1005067206346071</v>
+        <v>0.1053599788431535</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4123033285140991</v>
+        <v>0.4125459492206573</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3982484936714172</v>
+        <v>0.4051845073699951</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3528472185134887</v>
+        <v>0.3610811531543731</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3496434688568115</v>
+        <v>0.3651995062828064</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0424840450286865</v>
+        <v>0.0413248538970947</v>
       </c>
       <c r="K6" t="n">
-        <v>17.66157174110413</v>
+        <v>18.30338549613953</v>
       </c>
       <c r="L6" t="n">
-        <v>1.105808973312378</v>
+        <v>1.107913970947266</v>
       </c>
       <c r="M6" t="n">
-        <v>2.927817106246948</v>
+        <v>3.061645984649658</v>
       </c>
       <c r="N6" t="n">
-        <v>4.474115610122681</v>
+        <v>4.710334300994873</v>
       </c>
       <c r="O6" t="n">
-        <v>0.184301495552063</v>
+        <v>0.1846523284912109</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4879695177078247</v>
+        <v>0.510274330774943</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7456859350204468</v>
+        <v>0.7850557168324789</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-095527</t>
+          <t>20250719-235905</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5775,22 +5775,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5800,10 +5800,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>

--- a/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-tiny_human_railway_animal.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-tiny_human_railway_animal.xlsx
@@ -591,56 +591,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="C2" t="n">
-        <v>36.45807576179504</v>
+        <v>49.70476293563843</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8100000023841858</v>
+        <v>0.8700000047683716</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0304603691284472</v>
+        <v>0.0310433502965325</v>
       </c>
       <c r="F2" t="n">
-        <v>0.662481427192688</v>
+        <v>0.6721983551979065</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6510761976242065</v>
+        <v>0.6573202610015869</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5961630344390869</v>
+        <v>0.5883639454841614</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6134405732154846</v>
+        <v>0.6059582233428955</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0304033756256103</v>
+        <v>0.0312976837158203</v>
       </c>
       <c r="K2" t="n">
-        <v>17.53352737426758</v>
+        <v>17.72143530845642</v>
       </c>
       <c r="L2" t="n">
-        <v>1.125787258148193</v>
+        <v>1.18540358543396</v>
       </c>
       <c r="M2" t="n">
-        <v>3.406899929046631</v>
+        <v>3.35572338104248</v>
       </c>
       <c r="N2" t="n">
-        <v>4.042019844055176</v>
+        <v>4.06971001625061</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1876312096913655</v>
+        <v>0.1975672642389933</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5678166548411051</v>
+        <v>0.5592872301737467</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6736699740091959</v>
+        <v>0.6782850027084351</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250720-043040</t>
+          <t>20250723-150841</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -712,56 +712,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C3" t="n">
-        <v>36.76114797592163</v>
+        <v>41.50866770744324</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7699999809265137</v>
+        <v>0.6600000262260437</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0308015805024366</v>
+        <v>0.0309942768466087</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6583503484725952</v>
+        <v>0.6629530191421509</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6390154361724854</v>
+        <v>0.6414666175842285</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5856920480728149</v>
+        <v>0.5970532894134521</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5970742106437683</v>
+        <v>0.6049035787582397</v>
       </c>
       <c r="J3" t="n">
-        <v>0.030773639678955</v>
+        <v>0.0391483306884765</v>
       </c>
       <c r="K3" t="n">
-        <v>17.62287211418152</v>
+        <v>17.53318572044373</v>
       </c>
       <c r="L3" t="n">
-        <v>1.131823301315308</v>
+        <v>1.155514478683472</v>
       </c>
       <c r="M3" t="n">
-        <v>3.252345561981201</v>
+        <v>3.355695486068726</v>
       </c>
       <c r="N3" t="n">
-        <v>4.091201782226562</v>
+        <v>3.846954822540283</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1886372168858846</v>
+        <v>0.1925857464472452</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5420575936635336</v>
+        <v>0.5592825810114542</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6818669637044271</v>
+        <v>0.6411591370900472</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250720-043232</t>
+          <t>20250723-151046</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -833,56 +833,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="C4" t="n">
-        <v>37.77942299842834</v>
+        <v>54.87845158576965</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7699999809265137</v>
+        <v>0.8100000023841858</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0308628344754559</v>
+        <v>0.0307233234834388</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6553407311439514</v>
+        <v>0.6762324571609497</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6433175206184387</v>
+        <v>0.6618360280990601</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5904541015625</v>
+        <v>0.6195836067199707</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6071197986602783</v>
+        <v>0.6261422038078308</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0465865135192871</v>
+        <v>0.0332207679748535</v>
       </c>
       <c r="K4" t="n">
-        <v>17.45291924476624</v>
+        <v>17.39814329147339</v>
       </c>
       <c r="L4" t="n">
-        <v>1.179269313812256</v>
+        <v>1.167566299438477</v>
       </c>
       <c r="M4" t="n">
-        <v>3.370163202285767</v>
+        <v>3.313072443008423</v>
       </c>
       <c r="N4" t="n">
-        <v>4.00613260269165</v>
+        <v>3.980023145675659</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1965448856353759</v>
+        <v>0.1945943832397461</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5616938670476278</v>
+        <v>0.5521787405014038</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.667688767115275</v>
+        <v>0.6633371909459432</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250720-043423</t>
+          <t>20250723-151242</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -954,56 +954,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="C5" t="n">
-        <v>37.59170246124268</v>
+        <v>47.60109090805054</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8100000023841858</v>
+        <v>0.6600000262260437</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0307358098686287</v>
+        <v>0.0303377790583504</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6582750082015991</v>
+        <v>0.6839768886566162</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6393684148788452</v>
+        <v>0.674805760383606</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5846055746078491</v>
+        <v>0.6192440986633301</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5983153581619263</v>
+        <v>0.6305025815963745</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0281958580017089</v>
+        <v>0.0327851772308349</v>
       </c>
       <c r="K5" t="n">
-        <v>17.36346197128296</v>
+        <v>17.37134480476379</v>
       </c>
       <c r="L5" t="n">
-        <v>1.164453983306885</v>
+        <v>1.136852025985718</v>
       </c>
       <c r="M5" t="n">
-        <v>3.236575603485107</v>
+        <v>3.353680849075317</v>
       </c>
       <c r="N5" t="n">
-        <v>3.91330885887146</v>
+        <v>3.966732740402222</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1940756638844808</v>
+        <v>0.1894753376642863</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5394292672475179</v>
+        <v>0.5589468081792196</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6522181431452433</v>
+        <v>0.6611221234003702</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250720-043616</t>
+          <t>20250723-151452</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1075,56 +1075,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="C6" t="n">
-        <v>37.24337792396545</v>
+        <v>46.91587328910828</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7699999809265137</v>
+        <v>0.8100000023841858</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0304783528004217</v>
+        <v>0.0302590131759643</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6758353710174561</v>
+        <v>0.6860554218292236</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6658546328544617</v>
+        <v>0.6670454740524292</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6186037659645081</v>
+        <v>0.6210078001022339</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6301876306533813</v>
+        <v>0.6314815282821655</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0331566333770751</v>
+        <v>0.032947301864624</v>
       </c>
       <c r="K6" t="n">
-        <v>17.36075520515442</v>
+        <v>17.37955021858215</v>
       </c>
       <c r="L6" t="n">
-        <v>1.204114198684692</v>
+        <v>1.193555593490601</v>
       </c>
       <c r="M6" t="n">
-        <v>3.208827495574951</v>
+        <v>3.307286500930786</v>
       </c>
       <c r="N6" t="n">
-        <v>4.013649225234985</v>
+        <v>4.010801076889038</v>
       </c>
       <c r="O6" t="n">
-        <v>0.200685699780782</v>
+        <v>0.1989259322484334</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5348045825958252</v>
+        <v>0.5512144168217977</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6689415375391642</v>
+        <v>0.668466846148173</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250720-043808</t>
+          <t>20250723-151654</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1362,56 +1362,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="C2" t="n">
-        <v>54.70855712890625</v>
+        <v>74.69055557250977</v>
       </c>
       <c r="D2" t="n">
         <v>1.879999995231628</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1589160424853683</v>
+        <v>0.1571008137294224</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6471351385116577</v>
+        <v>0.6801127195358276</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6354399919509888</v>
+        <v>0.6635236740112305</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5758244395256042</v>
+        <v>0.616192638874054</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5798583030700684</v>
+        <v>0.5801909565925598</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0643284320831298</v>
+        <v>0.06351256370544429</v>
       </c>
       <c r="K2" t="n">
-        <v>27.1875069141388</v>
+        <v>27.22650456428528</v>
       </c>
       <c r="L2" t="n">
-        <v>1.388995409011841</v>
+        <v>1.634926080703735</v>
       </c>
       <c r="M2" t="n">
-        <v>3.897054433822632</v>
+        <v>3.850879669189453</v>
       </c>
       <c r="N2" t="n">
-        <v>5.842442512512207</v>
+        <v>5.986278057098389</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2314992348353068</v>
+        <v>0.2724876801172892</v>
       </c>
       <c r="P2" t="n">
-        <v>0.649509072303772</v>
+        <v>0.6418132781982422</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9737404187520344</v>
+        <v>0.997713009516398</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-081243</t>
+          <t>20250721-133615</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1483,56 +1483,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="C3" t="n">
-        <v>55.02376770973206</v>
+        <v>76.00908660888672</v>
       </c>
       <c r="D3" t="n">
         <v>1.809999942779541</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1626946947990207</v>
+        <v>0.159799727526578</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6860097050666809</v>
+        <v>0.7194790840148926</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6350861787796021</v>
+        <v>0.6916053295135498</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5735282897949219</v>
+        <v>0.6232385039329529</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5904849767684937</v>
+        <v>0.6402603983879089</v>
       </c>
       <c r="J3" t="n">
-        <v>0.06573128700256339</v>
+        <v>0.0662269592285156</v>
       </c>
       <c r="K3" t="n">
-        <v>27.18326091766357</v>
+        <v>21.50003790855408</v>
       </c>
       <c r="L3" t="n">
-        <v>1.697369813919067</v>
+        <v>1.394912481307983</v>
       </c>
       <c r="M3" t="n">
-        <v>4.266744613647461</v>
+        <v>4.323253631591797</v>
       </c>
       <c r="N3" t="n">
-        <v>5.909223318099976</v>
+        <v>6.14378547668457</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2828949689865112</v>
+        <v>0.2324854135513305</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7111241022745768</v>
+        <v>0.7205422719319662</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9848705530166626</v>
+        <v>1.023964246114095</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-081521</t>
+          <t>20250721-133912</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1604,56 +1604,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C4" t="n">
-        <v>59.45315217971802</v>
+        <v>60.69062972068787</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1.809999942779541</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1581056839277764</v>
+        <v>0.1563957256655539</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7022587656974792</v>
+        <v>0.6779159307479858</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6771821975708008</v>
+        <v>0.6559498310089111</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6161133050918579</v>
+        <v>0.6124357581138611</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6249626874923706</v>
+        <v>0.5809080600738525</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0636425018310546</v>
+        <v>0.06547379493713371</v>
       </c>
       <c r="K4" t="n">
-        <v>27.01202297210693</v>
+        <v>21.35423231124878</v>
       </c>
       <c r="L4" t="n">
-        <v>1.421429395675659</v>
+        <v>1.367000341415405</v>
       </c>
       <c r="M4" t="n">
-        <v>3.933868885040283</v>
+        <v>3.976807355880737</v>
       </c>
       <c r="N4" t="n">
-        <v>5.932942390441895</v>
+        <v>6.440245866775513</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2369048992792765</v>
+        <v>0.2278333902359008</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6556448141733805</v>
+        <v>0.6628012259801229</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9888237317403158</v>
+        <v>1.073374311129252</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-081759</t>
+          <t>20250721-134205</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1725,56 +1725,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>52.22027373313904</v>
+        <v>61.3051552772522</v>
       </c>
       <c r="D5" t="n">
         <v>1.809999942779541</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1581030946511488</v>
+        <v>0.1586606617896787</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6784218549728394</v>
+        <v>0.686083197593689</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6526472568511963</v>
+        <v>0.6538863778114319</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5813831686973572</v>
+        <v>0.6038768291473389</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5865321755409241</v>
+        <v>0.5941597819328308</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06695199012756339</v>
+        <v>0.087975263595581</v>
       </c>
       <c r="K5" t="n">
-        <v>27.44209146499633</v>
+        <v>27.38161540031433</v>
       </c>
       <c r="L5" t="n">
-        <v>1.717432260513306</v>
+        <v>1.734646797180176</v>
       </c>
       <c r="M5" t="n">
-        <v>3.863162755966187</v>
+        <v>3.894954204559326</v>
       </c>
       <c r="N5" t="n">
-        <v>5.975803136825562</v>
+        <v>5.916398286819458</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2862387100855509</v>
+        <v>0.2891077995300293</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6438604593276978</v>
+        <v>0.6491590340932211</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9959671894709268</v>
+        <v>0.9860663811365764</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-082040</t>
+          <t>20250721-134428</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1846,56 +1846,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="C6" t="n">
-        <v>53.0766978263855</v>
+        <v>77.24161911010742</v>
       </c>
       <c r="D6" t="n">
         <v>1.879999995231628</v>
       </c>
       <c r="E6" t="n">
-        <v>0.154566865448558</v>
+        <v>0.1589194708650216</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6390262246131897</v>
+        <v>0.7151864767074585</v>
       </c>
       <c r="G6" t="n">
-        <v>0.614453911781311</v>
+        <v>0.6873548030853271</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5698897838592529</v>
+        <v>0.6242334246635437</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5648249387741089</v>
+        <v>0.6041175127029419</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07105851173400871</v>
+        <v>0.0661466121673584</v>
       </c>
       <c r="K6" t="n">
-        <v>27.47228503227234</v>
+        <v>21.726243019104</v>
       </c>
       <c r="L6" t="n">
-        <v>1.435880899429321</v>
+        <v>1.401013612747192</v>
       </c>
       <c r="M6" t="n">
-        <v>3.947920322418213</v>
+        <v>3.909031867980957</v>
       </c>
       <c r="N6" t="n">
-        <v>5.896742820739746</v>
+        <v>6.26063084602356</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2393134832382202</v>
+        <v>0.2335022687911987</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6579867204030355</v>
+        <v>0.6515053113301595</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.982790470123291</v>
+        <v>1.04343847433726</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-082315</t>
+          <t>20250721-134712</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2133,56 +2133,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="C2" t="n">
-        <v>49.91915106773376</v>
+        <v>78.37969398498535</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1306037129017344</v>
+        <v>0.1299856395825095</v>
       </c>
       <c r="F2" t="n">
-        <v>0.559049129486084</v>
+        <v>0.6549398899078369</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5527282953262329</v>
+        <v>0.6439425945281982</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4697427153587341</v>
+        <v>0.578042209148407</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3952880799770355</v>
+        <v>0.3882554769515991</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0636677742004394</v>
+        <v>0.0554981231689453</v>
       </c>
       <c r="K2" t="n">
-        <v>23.90707659721375</v>
+        <v>24.54449033737182</v>
       </c>
       <c r="L2" t="n">
-        <v>1.508503913879394</v>
+        <v>1.199472188949585</v>
       </c>
       <c r="M2" t="n">
-        <v>4.865602731704712</v>
+        <v>4.816797494888306</v>
       </c>
       <c r="N2" t="n">
-        <v>8.234938383102417</v>
+        <v>8.145910739898682</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2514173189798991</v>
+        <v>0.1999120314915975</v>
       </c>
       <c r="P2" t="n">
-        <v>0.810933788617452</v>
+        <v>0.8027995824813843</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.37248973051707</v>
+        <v>1.357651789983114</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-142200</t>
+          <t>20250721-202417</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2254,56 +2254,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="C3" t="n">
-        <v>51.65755534172058</v>
+        <v>67.21129631996155</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9300000071525574</v>
+        <v>0.8700000047683716</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1310891143414152</v>
+        <v>0.1288171511191826</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5459414124488831</v>
+        <v>0.596813440322876</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5362982749938965</v>
+        <v>0.6098102927207947</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4551478028297424</v>
+        <v>0.5704867839813232</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3675386011600494</v>
+        <v>0.4246286451816559</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0529663562774658</v>
+        <v>0.0514490604400634</v>
       </c>
       <c r="K3" t="n">
-        <v>24.03808355331421</v>
+        <v>23.98268604278564</v>
       </c>
       <c r="L3" t="n">
-        <v>1.209650993347168</v>
+        <v>1.196269273757935</v>
       </c>
       <c r="M3" t="n">
-        <v>4.883680820465088</v>
+        <v>4.797978162765503</v>
       </c>
       <c r="N3" t="n">
-        <v>8.329090118408203</v>
+        <v>8.070831537246704</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2016084988911946</v>
+        <v>0.1993782122929891</v>
       </c>
       <c r="P3" t="n">
-        <v>0.813946803410848</v>
+        <v>0.7996630271275839</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.388181686401367</v>
+        <v>1.345138589541117</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-142431</t>
+          <t>20250721-202717</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -2375,56 +2375,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>109</v>
+        <v>174</v>
       </c>
       <c r="C4" t="n">
-        <v>48.58184170722961</v>
+        <v>74.62911891937256</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8700000047683716</v>
+        <v>0.9300000071525574</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1327024818560398</v>
+        <v>0.1299994060362892</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5467156171798706</v>
+        <v>0.5365243554115295</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5277916193008423</v>
+        <v>0.5370291471481323</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4404500424861908</v>
+        <v>0.4425767064094543</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3918160200119018</v>
+        <v>0.4482683539390564</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0454730987548828</v>
+        <v>0.0549342632293701</v>
       </c>
       <c r="K4" t="n">
-        <v>24.26550436019897</v>
+        <v>24.57332587242126</v>
       </c>
       <c r="L4" t="n">
-        <v>1.171926259994507</v>
+        <v>1.216620683670044</v>
       </c>
       <c r="M4" t="n">
-        <v>5.20591926574707</v>
+        <v>5.134363412857056</v>
       </c>
       <c r="N4" t="n">
-        <v>8.412823438644409</v>
+        <v>8.079388618469238</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1953210433324178</v>
+        <v>0.2027701139450073</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8676532109578451</v>
+        <v>0.8557272354761759</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.402137239774068</v>
+        <v>1.346564769744873</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-142704</t>
+          <t>20250721-203004</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2496,56 +2496,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>114</v>
+        <v>199</v>
       </c>
       <c r="C5" t="n">
-        <v>50.35176086425781</v>
+        <v>84.53961277008057</v>
       </c>
       <c r="D5" t="n">
         <v>0.9300000071525574</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1304332373435036</v>
+        <v>0.1286016948259056</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6653591394424438</v>
+        <v>0.6411560773849487</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6573480367660522</v>
+        <v>0.6218426823616028</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5877595543861389</v>
+        <v>0.5233088135719299</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4144032597541809</v>
+        <v>0.4465329051017761</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0466084480285644</v>
+        <v>0.0567004680633544</v>
       </c>
       <c r="K5" t="n">
-        <v>24.28187608718872</v>
+        <v>24.32265830039978</v>
       </c>
       <c r="L5" t="n">
-        <v>1.211792469024658</v>
+        <v>1.211456060409546</v>
       </c>
       <c r="M5" t="n">
-        <v>5.161906957626343</v>
+        <v>4.746617555618286</v>
       </c>
       <c r="N5" t="n">
-        <v>8.306535720825195</v>
+        <v>8.178431749343872</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2019654115041097</v>
+        <v>0.2019093434015909</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8603178262710571</v>
+        <v>0.791102925936381</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.384422620137532</v>
+        <v>1.363071958223979</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-142933</t>
+          <t>20250721-203300</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2617,56 +2617,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="C6" t="n">
-        <v>48.48200058937073</v>
+        <v>55.96493220329285</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8199999928474426</v>
+        <v>0.8700000047683716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1324840707516451</v>
+        <v>0.1310019825780113</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5390551090240479</v>
+        <v>0.5962384343147278</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5356808304786682</v>
+        <v>0.6210411787033081</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4793267548084259</v>
+        <v>0.5804635882377625</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4114625155925751</v>
+        <v>0.3907530009746551</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0632970333099365</v>
+        <v>0.06830978393554681</v>
       </c>
       <c r="K6" t="n">
-        <v>24.14178419113159</v>
+        <v>18.63409066200256</v>
       </c>
       <c r="L6" t="n">
-        <v>1.506988286972046</v>
+        <v>1.237351894378662</v>
       </c>
       <c r="M6" t="n">
-        <v>4.808172225952148</v>
+        <v>4.821367025375366</v>
       </c>
       <c r="N6" t="n">
-        <v>8.24954628944397</v>
+        <v>8.262760639190674</v>
       </c>
       <c r="O6" t="n">
-        <v>0.251164714495341</v>
+        <v>0.206225315729777</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8013620376586914</v>
+        <v>0.8035611708958944</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.374924381573995</v>
+        <v>1.377126773198446</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-143205</t>
+          <t>20250721-203605</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2904,56 +2904,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="C2" t="n">
-        <v>79.4699764251709</v>
+        <v>104.057014465332</v>
       </c>
       <c r="D2" t="n">
-        <v>6.440000057220459</v>
+        <v>6.480000019073486</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2948786417643229</v>
+        <v>0.2963021137570374</v>
       </c>
       <c r="F2" t="n">
-        <v>0.614651083946228</v>
+        <v>0.7044764161109924</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5833204388618469</v>
+        <v>0.66754549741745</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4926593899726867</v>
+        <v>0.6294456720352173</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3052634298801422</v>
+        <v>0.3689831495285034</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09826493263244621</v>
+        <v>0.1144497394561767</v>
       </c>
       <c r="K2" t="n">
-        <v>80.53887820243835</v>
+        <v>74.56428933143616</v>
       </c>
       <c r="L2" t="n">
-        <v>1.958956956863404</v>
+        <v>2.385088443756104</v>
       </c>
       <c r="M2" t="n">
-        <v>6.586667060852051</v>
+        <v>6.304755449295044</v>
       </c>
       <c r="N2" t="n">
-        <v>14.06648659706116</v>
+        <v>14.10544991493225</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3264928261439005</v>
+        <v>0.3975147406260172</v>
       </c>
       <c r="P2" t="n">
-        <v>1.097777843475342</v>
+        <v>1.050792574882507</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.344414432843526</v>
+        <v>2.350908319155375</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-195910</t>
+          <t>20250722-024238</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3025,56 +3025,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="C3" t="n">
-        <v>77.62743735313416</v>
+        <v>97.3556468486786</v>
       </c>
       <c r="D3" t="n">
-        <v>6.440000057220459</v>
+        <v>6.480000019073486</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2982016790897474</v>
+        <v>0.2974340366802627</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6392878890037537</v>
+        <v>0.6250336766242981</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6243941783905029</v>
+        <v>0.6151576042175293</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5610353946685791</v>
+        <v>0.5112179517745972</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3256377875804901</v>
+        <v>0.3186087906360626</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1083700656890869</v>
+        <v>0.1076033115386962</v>
       </c>
       <c r="K3" t="n">
-        <v>80.823734998703</v>
+        <v>74.94038248062134</v>
       </c>
       <c r="L3" t="n">
-        <v>2.369732856750488</v>
+        <v>2.321122646331787</v>
       </c>
       <c r="M3" t="n">
-        <v>6.607530355453491</v>
+        <v>6.334118843078613</v>
       </c>
       <c r="N3" t="n">
-        <v>14.1459481716156</v>
+        <v>14.01608347892761</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3949554761250813</v>
+        <v>0.3868537743886311</v>
       </c>
       <c r="P3" t="n">
-        <v>1.101255059242248</v>
+        <v>1.055686473846436</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3576580286026</v>
+        <v>2.336013913154602</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-200345</t>
+          <t>20250722-024737</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3146,56 +3146,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="C4" t="n">
-        <v>71.32682132720947</v>
+        <v>134.2296621799469</v>
       </c>
       <c r="D4" t="n">
-        <v>6.440000057220459</v>
+        <v>6.480000019073486</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2987134892206926</v>
+        <v>0.2983377201040995</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6171367764472961</v>
+        <v>0.6708962917327881</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5992616415023804</v>
+        <v>0.6362783908843994</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5191515684127808</v>
+        <v>0.5337405800819397</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3346635103225708</v>
+        <v>0.3224110305309295</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1014385223388671</v>
+        <v>0.1216733455657959</v>
       </c>
       <c r="K4" t="n">
-        <v>74.65886282920837</v>
+        <v>74.07824444770813</v>
       </c>
       <c r="L4" t="n">
-        <v>2.27964973449707</v>
+        <v>2.330559253692627</v>
       </c>
       <c r="M4" t="n">
-        <v>6.808593034744263</v>
+        <v>6.269084692001343</v>
       </c>
       <c r="N4" t="n">
-        <v>14.10869860649109</v>
+        <v>14.29693937301636</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3799416224161784</v>
+        <v>0.3884265422821045</v>
       </c>
       <c r="P4" t="n">
-        <v>1.13476550579071</v>
+        <v>1.04484744866689</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.351449767748515</v>
+        <v>2.38282322883606</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-200817</t>
+          <t>20250722-025229</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3267,56 +3267,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="C5" t="n">
-        <v>81.91268277168274</v>
+        <v>127.9941735267639</v>
       </c>
       <c r="D5" t="n">
-        <v>6.480000019073486</v>
+        <v>6.519999980926514</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2992372721956487</v>
+        <v>0.2997126320134038</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6301993131637573</v>
+        <v>0.6678870916366577</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5995290279388428</v>
+        <v>0.6291494369506836</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5269789099693298</v>
+        <v>0.5610572695732117</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3343516886234283</v>
+        <v>0.3360804319381714</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1065397262573242</v>
+        <v>0.1205301284790039</v>
       </c>
       <c r="K5" t="n">
-        <v>81.08261108398438</v>
+        <v>80.96190619468689</v>
       </c>
       <c r="L5" t="n">
-        <v>2.009196043014526</v>
+        <v>2.322121620178223</v>
       </c>
       <c r="M5" t="n">
-        <v>6.6134934425354</v>
+        <v>6.586496829986572</v>
       </c>
       <c r="N5" t="n">
-        <v>14.22904300689697</v>
+        <v>13.72413039207458</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3348660071690877</v>
+        <v>0.3870202700297038</v>
       </c>
       <c r="P5" t="n">
-        <v>1.102248907089233</v>
+        <v>1.097749471664429</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.371507167816162</v>
+        <v>2.287355065345764</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-201238</t>
+          <t>20250722-025738</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3388,56 +3388,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>109</v>
+        <v>184</v>
       </c>
       <c r="C6" t="n">
-        <v>74.99464440345764</v>
+        <v>127.044709444046</v>
       </c>
       <c r="D6" t="n">
         <v>6.480000019073486</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2961866221296678</v>
+        <v>0.2999549521052319</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6213536262512207</v>
+        <v>0.6428007483482361</v>
       </c>
       <c r="G6" t="n">
-        <v>0.599226176738739</v>
+        <v>0.635802149772644</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5230228304862976</v>
+        <v>0.5437143445014954</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3286988735198974</v>
+        <v>0.371466726064682</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1051743030548095</v>
+        <v>0.1398916244506836</v>
       </c>
       <c r="K6" t="n">
-        <v>81.32683682441711</v>
+        <v>81.4278998374939</v>
       </c>
       <c r="L6" t="n">
-        <v>2.010254859924316</v>
+        <v>2.393152952194214</v>
       </c>
       <c r="M6" t="n">
-        <v>6.614840269088745</v>
+        <v>6.554213285446167</v>
       </c>
       <c r="N6" t="n">
-        <v>14.55279970169067</v>
+        <v>14.22862958908081</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3350424766540527</v>
+        <v>0.3988588253657023</v>
       </c>
       <c r="P6" t="n">
-        <v>1.102473378181458</v>
+        <v>1.092368880907695</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.425466616948446</v>
+        <v>2.371438264846802</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-201715</t>
+          <t>20250722-030301</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3675,56 +3675,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="C2" t="n">
-        <v>97.84995794296265</v>
+        <v>136.1171493530273</v>
       </c>
       <c r="D2" t="n">
-        <v>5.739999771118164</v>
+        <v>5.730000019073486</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1658405279941695</v>
+        <v>0.1651751527834178</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5834954977035522</v>
+        <v>0.5861800312995911</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5879294276237488</v>
+        <v>0.5899001359939575</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5622175931930542</v>
+        <v>0.5703705549240112</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5137215256690979</v>
+        <v>0.5637310743331909</v>
       </c>
       <c r="J2" t="n">
-        <v>0.065936803817749</v>
+        <v>0.0653994083404541</v>
       </c>
       <c r="K2" t="n">
-        <v>28.7547128200531</v>
+        <v>28.8108458518982</v>
       </c>
       <c r="L2" t="n">
-        <v>2.06320333480835</v>
+        <v>1.745194435119629</v>
       </c>
       <c r="M2" t="n">
-        <v>4.048621416091919</v>
+        <v>4.030714511871338</v>
       </c>
       <c r="N2" t="n">
-        <v>7.19835352897644</v>
+        <v>6.861128568649292</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3438672224680583</v>
+        <v>0.2908657391866048</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6747702360153198</v>
+        <v>0.6717857519785563</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.19972558816274</v>
+        <v>1.143521428108215</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250719-125136</t>
+          <t>20250722-203012</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3796,56 +3796,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>73.97748851776123</v>
+        <v>139.0170681476593</v>
       </c>
       <c r="D3" t="n">
-        <v>5.730000019073486</v>
+        <v>5.889999866485596</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1649855352365053</v>
+        <v>0.1666734242559078</v>
       </c>
       <c r="F3" t="n">
-        <v>0.413469910621643</v>
+        <v>0.6734703779220581</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4130900800228119</v>
+        <v>0.6652718782424927</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4124080538749695</v>
+        <v>0.6398103833198547</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4035665094852447</v>
+        <v>0.5845951437950134</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0664279460906982</v>
+        <v>0.0665464401245117</v>
       </c>
       <c r="K3" t="n">
-        <v>23.06320762634277</v>
+        <v>23.04127502441406</v>
       </c>
       <c r="L3" t="n">
-        <v>1.776934862136841</v>
+        <v>1.817973375320434</v>
       </c>
       <c r="M3" t="n">
-        <v>3.957690715789795</v>
+        <v>4.020785093307495</v>
       </c>
       <c r="N3" t="n">
-        <v>6.854444980621338</v>
+        <v>6.802385091781616</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2961558103561401</v>
+        <v>0.3029955625534057</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6596151192982992</v>
+        <v>0.6701308488845825</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.142407496770223</v>
+        <v>1.133730848630269</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250719-125456</t>
+          <t>20250722-203410</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3917,56 +3917,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>119</v>
+        <v>199</v>
       </c>
       <c r="C4" t="n">
-        <v>81.5395143032074</v>
+        <v>135.3100383281708</v>
       </c>
       <c r="D4" t="n">
-        <v>5.730000019073486</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1642913237339308</v>
+        <v>0.1650188400517756</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4802051782608032</v>
+        <v>0.6498224139213562</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4781227111816406</v>
+        <v>0.5947351455688477</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4612117111682892</v>
+        <v>0.5716078281402588</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4560591578483581</v>
+        <v>0.548012375831604</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0637576580047607</v>
+        <v>0.0651500225067138</v>
       </c>
       <c r="K4" t="n">
-        <v>23.13473129272461</v>
+        <v>28.91837668418884</v>
       </c>
       <c r="L4" t="n">
-        <v>1.741113662719727</v>
+        <v>1.759001016616821</v>
       </c>
       <c r="M4" t="n">
-        <v>3.949750661849976</v>
+        <v>3.958923816680908</v>
       </c>
       <c r="N4" t="n">
-        <v>6.823941230773926</v>
+        <v>6.859610795974731</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2901856104532878</v>
+        <v>0.2931668361028035</v>
       </c>
       <c r="P4" t="n">
-        <v>0.658291776974996</v>
+        <v>0.6598206361134847</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.137323538462321</v>
+        <v>1.143268465995789</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250719-125752</t>
+          <t>20250722-203811</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4038,56 +4038,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="C5" t="n">
-        <v>73.67531204223633</v>
+        <v>133.4723148345947</v>
       </c>
       <c r="D5" t="n">
         <v>5.730000019073486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1652178654976941</v>
+        <v>0.166070575091108</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4768457412719726</v>
+        <v>0.663891613483429</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4723275601863861</v>
+        <v>0.6670433282852173</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4424610137939453</v>
+        <v>0.638307511806488</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3765975832939148</v>
+        <v>0.5911019444465637</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06755566596984861</v>
+        <v>0.0657386779785156</v>
       </c>
       <c r="K5" t="n">
-        <v>28.76229119300842</v>
+        <v>22.95835185050964</v>
       </c>
       <c r="L5" t="n">
-        <v>2.053828001022339</v>
+        <v>1.770256519317627</v>
       </c>
       <c r="M5" t="n">
-        <v>3.891594648361206</v>
+        <v>3.962921619415283</v>
       </c>
       <c r="N5" t="n">
-        <v>6.880436897277832</v>
+        <v>6.786395311355591</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3423046668370564</v>
+        <v>0.2950427532196045</v>
       </c>
       <c r="P5" t="n">
-        <v>0.648599108060201</v>
+        <v>0.6604869365692139</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.146739482879639</v>
+        <v>1.131065885225932</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250719-130055</t>
+          <t>20250722-204209</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4159,56 +4159,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="C6" t="n">
-        <v>104.6239199638367</v>
+        <v>134.9329006671906</v>
       </c>
       <c r="D6" t="n">
-        <v>5.730000019073486</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1670928193418771</v>
+        <v>0.1646462385378889</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5347345471382141</v>
+        <v>0.635337233543396</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5295642018318176</v>
+        <v>0.633036732673645</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4964151382446289</v>
+        <v>0.603856086730957</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4713392853736877</v>
+        <v>0.5751820802688599</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06496262550354</v>
+        <v>0.0706899166107177</v>
       </c>
       <c r="K6" t="n">
-        <v>22.75575304031372</v>
+        <v>28.49136328697205</v>
       </c>
       <c r="L6" t="n">
-        <v>1.789566278457642</v>
+        <v>1.822126865386963</v>
       </c>
       <c r="M6" t="n">
-        <v>4.040817260742188</v>
+        <v>3.984463691711426</v>
       </c>
       <c r="N6" t="n">
-        <v>6.809996366500855</v>
+        <v>6.924727201461792</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2982610464096069</v>
+        <v>0.3036878108978271</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6734695434570312</v>
+        <v>0.6640772819519043</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.134999394416809</v>
+        <v>1.154121200243632</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250719-130351</t>
+          <t>20250722-204604</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4446,56 +4446,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>124</v>
+        <v>199</v>
       </c>
       <c r="C2" t="n">
-        <v>62.70809245109558</v>
+        <v>94.97096371650696</v>
       </c>
       <c r="D2" t="n">
-        <v>3.559999942779541</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1048330683862009</v>
+        <v>0.1048001644000335</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4830430150032043</v>
+        <v>0.5877963900566101</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4818252325057983</v>
+        <v>0.5871404409408569</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4656838476657867</v>
+        <v>0.5566688179969788</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4534772336483001</v>
+        <v>0.5506567358970642</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0423731803894043</v>
+        <v>0.0430133342742919</v>
       </c>
       <c r="K2" t="n">
-        <v>18.28100419044494</v>
+        <v>18.52208375930786</v>
       </c>
       <c r="L2" t="n">
-        <v>1.24070143699646</v>
+        <v>1.276345491409302</v>
       </c>
       <c r="M2" t="n">
-        <v>2.963818073272705</v>
+        <v>2.99981427192688</v>
       </c>
       <c r="N2" t="n">
-        <v>4.363518238067627</v>
+        <v>4.397125959396362</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2067835728327433</v>
+        <v>0.2127242485682169</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4939696788787842</v>
+        <v>0.4999690453211466</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7272530396779379</v>
+        <v>0.7328543265660604</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250719-192628</t>
+          <t>20250723-040832</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4567,56 +4567,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>119</v>
+        <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>59.37469696998596</v>
+        <v>97.15802907943726</v>
       </c>
       <c r="D3" t="n">
-        <v>3.319999933242798</v>
+        <v>3.380000114440918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1043752862625762</v>
+        <v>0.1037715272088745</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4798779785633087</v>
+        <v>0.6270030736923218</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4810023009777069</v>
+        <v>0.6116017699241638</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4688295423984527</v>
+        <v>0.5815740823745728</v>
       </c>
       <c r="I3" t="n">
-        <v>0.431626558303833</v>
+        <v>0.5740866661071777</v>
       </c>
       <c r="J3" t="n">
-        <v>0.041750431060791</v>
+        <v>0.0414395332336425</v>
       </c>
       <c r="K3" t="n">
-        <v>18.5976037979126</v>
+        <v>18.35482907295227</v>
       </c>
       <c r="L3" t="n">
-        <v>1.209543943405151</v>
+        <v>1.258665800094604</v>
       </c>
       <c r="M3" t="n">
-        <v>3.271190881729126</v>
+        <v>3.031445026397705</v>
       </c>
       <c r="N3" t="n">
-        <v>4.444772481918335</v>
+        <v>4.407848358154297</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2015906572341919</v>
+        <v>0.2097776333491007</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5451984802881876</v>
+        <v>0.5052408377329508</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7407954136530558</v>
+        <v>0.7346413930257162</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250719-192849</t>
+          <t>20250723-041126</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4688,56 +4688,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>119</v>
+        <v>199</v>
       </c>
       <c r="C4" t="n">
-        <v>58.50276589393616</v>
+        <v>98.61102604866028</v>
       </c>
       <c r="D4" t="n">
-        <v>3.339999914169312</v>
+        <v>3.450000047683716</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1045664318469391</v>
+        <v>0.1048988660975316</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5468660593032837</v>
+        <v>0.5754732489585876</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5472531914710999</v>
+        <v>0.5766698122024536</v>
       </c>
       <c r="H4" t="n">
-        <v>0.518307626247406</v>
+        <v>0.5433073043823242</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4953703582286834</v>
+        <v>0.5484713912010193</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0428197383880615</v>
+        <v>0.0443575382232666</v>
       </c>
       <c r="K4" t="n">
-        <v>18.13897347450256</v>
+        <v>18.5571346282959</v>
       </c>
       <c r="L4" t="n">
-        <v>1.277062654495239</v>
+        <v>1.27245283126831</v>
       </c>
       <c r="M4" t="n">
-        <v>2.951371431350708</v>
+        <v>3.011070966720581</v>
       </c>
       <c r="N4" t="n">
-        <v>4.376526832580566</v>
+        <v>4.551193714141846</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2128437757492065</v>
+        <v>0.2120754718780517</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4918952385584513</v>
+        <v>0.5018451611200968</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7294211387634277</v>
+        <v>0.7585322856903076</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250719-193107</t>
+          <t>20250723-041422</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4809,56 +4809,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="C5" t="n">
-        <v>53.0546019077301</v>
+        <v>95.96088886260986</v>
       </c>
       <c r="D5" t="n">
-        <v>3.400000095367432</v>
+        <v>3.380000114440918</v>
       </c>
       <c r="E5" t="n">
-        <v>0.104106618723738</v>
+        <v>0.1045521204196028</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4218621551990509</v>
+        <v>0.6473498344421387</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4191117882728576</v>
+        <v>0.6237092018127441</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4090718030929565</v>
+        <v>0.5859754681587219</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3954173922538757</v>
+        <v>0.5669323801994324</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0511913299560546</v>
+        <v>0.0428762435913085</v>
       </c>
       <c r="K5" t="n">
-        <v>18.45261263847351</v>
+        <v>18.3447687625885</v>
       </c>
       <c r="L5" t="n">
-        <v>1.228314876556396</v>
+        <v>1.290494918823242</v>
       </c>
       <c r="M5" t="n">
-        <v>2.931522607803345</v>
+        <v>2.95409369468689</v>
       </c>
       <c r="N5" t="n">
-        <v>4.364612340927124</v>
+        <v>4.391831874847412</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2047191460927327</v>
+        <v>0.2150824864705403</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4885871013005574</v>
+        <v>0.4923489491144816</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7274353901545206</v>
+        <v>0.7319719791412354</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250719-193324</t>
+          <t>20250723-041720</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4930,56 +4930,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>154</v>
+        <v>199</v>
       </c>
       <c r="C6" t="n">
-        <v>75.38698315620422</v>
+        <v>96.63166213035583</v>
       </c>
       <c r="D6" t="n">
-        <v>3.369999885559082</v>
+        <v>3.450000047683716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1066695699444064</v>
+        <v>0.1047967127220115</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5707952976226807</v>
+        <v>0.5892661809921265</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5695808529853821</v>
+        <v>0.5869459509849548</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5357460379600525</v>
+        <v>0.5481494665145874</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5014727711677551</v>
+        <v>0.5347583293914795</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0434422492980957</v>
+        <v>0.0437536239624023</v>
       </c>
       <c r="K6" t="n">
-        <v>18.16665744781494</v>
+        <v>18.45687174797058</v>
       </c>
       <c r="L6" t="n">
-        <v>1.231808185577393</v>
+        <v>1.238555669784546</v>
       </c>
       <c r="M6" t="n">
-        <v>2.833969116210937</v>
+        <v>2.959306955337524</v>
       </c>
       <c r="N6" t="n">
-        <v>4.379346370697021</v>
+        <v>4.424213171005249</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2053013642628987</v>
+        <v>0.2064259449640909</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4723281860351562</v>
+        <v>0.4932178258895874</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7298910617828369</v>
+        <v>0.7373688618342081</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250719-193536</t>
+          <t>20250723-042014</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5217,56 +5217,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="C2" t="n">
-        <v>43.50282907485962</v>
+        <v>79.51230454444885</v>
       </c>
       <c r="D2" t="n">
         <v>2.230000019073486</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1045918486533908</v>
+        <v>0.1047092754038134</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3799217641353607</v>
+        <v>0.5743158459663391</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3800491988658905</v>
+        <v>0.5684853196144104</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3266389667987823</v>
+        <v>0.5190215706825256</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3315319120883941</v>
+        <v>0.5117236971855164</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0331640243530273</v>
+        <v>0.0394051074981689</v>
       </c>
       <c r="K2" t="n">
-        <v>17.83287024497986</v>
+        <v>12.01785230636597</v>
       </c>
       <c r="L2" t="n">
-        <v>1.095563888549805</v>
+        <v>1.151092290878296</v>
       </c>
       <c r="M2" t="n">
-        <v>3.093571186065674</v>
+        <v>2.97154688835144</v>
       </c>
       <c r="N2" t="n">
-        <v>4.603387594223023</v>
+        <v>4.668939352035522</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1825939814249674</v>
+        <v>0.1918487151463826</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5155951976776123</v>
+        <v>0.49525781472524</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.767231265703837</v>
+        <v>0.778156558672587</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250719-235026</t>
+          <t>20250723-094257</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5338,56 +5338,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C3" t="n">
-        <v>71.29575109481812</v>
+        <v>75.33236479759216</v>
       </c>
       <c r="D3" t="n">
-        <v>2.220000028610229</v>
+        <v>2.319999933242798</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1048318161361518</v>
+        <v>0.1032052809599215</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6226320266723633</v>
+        <v>0.5699828863143921</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6399800777435303</v>
+        <v>0.5625791549682617</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5787913799285889</v>
+        <v>0.5084738731384277</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5305467247962952</v>
+        <v>0.428037017583847</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0406956672668457</v>
+        <v>0.0403544902801513</v>
       </c>
       <c r="K3" t="n">
-        <v>17.52231693267822</v>
+        <v>17.69667959213257</v>
       </c>
       <c r="L3" t="n">
-        <v>1.09441089630127</v>
+        <v>1.062662363052368</v>
       </c>
       <c r="M3" t="n">
-        <v>2.969051361083984</v>
+        <v>2.98746919631958</v>
       </c>
       <c r="N3" t="n">
-        <v>5.106841325759888</v>
+        <v>4.996368408203125</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1824018160502115</v>
+        <v>0.1771103938420613</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4948418935139974</v>
+        <v>0.49791153271993</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8511402209599813</v>
+        <v>0.8327280680338541</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250719-235229</t>
+          <t>20250723-094535</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5459,56 +5459,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="C4" t="n">
-        <v>45.5185878276825</v>
+        <v>79.82545900344849</v>
       </c>
       <c r="D4" t="n">
-        <v>2.220000028610229</v>
+        <v>2.609999895095825</v>
       </c>
       <c r="E4" t="n">
-        <v>0.103965866456338</v>
+        <v>0.1051408921054858</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4215139150619507</v>
+        <v>0.5314182639122009</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4159503281116485</v>
+        <v>0.5283846855163574</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3870499730110168</v>
+        <v>0.4687684774398803</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3849406838417053</v>
+        <v>0.4681791067123413</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0347070693969726</v>
+        <v>0.0422892570495605</v>
       </c>
       <c r="K4" t="n">
-        <v>18.15665459632873</v>
+        <v>17.74409055709839</v>
       </c>
       <c r="L4" t="n">
-        <v>1.061548709869385</v>
+        <v>1.124720096588135</v>
       </c>
       <c r="M4" t="n">
-        <v>3.121005535125732</v>
+        <v>2.960173606872559</v>
       </c>
       <c r="N4" t="n">
-        <v>4.591790437698364</v>
+        <v>4.951078176498413</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1769247849782308</v>
+        <v>0.1874533494313558</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5201675891876221</v>
+        <v>0.4933622678120931</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7652984062830607</v>
+        <v>0.8251796960830688</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250719-235459</t>
+          <t>20250723-094809</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5580,56 +5580,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>104</v>
+        <v>199</v>
       </c>
       <c r="C5" t="n">
-        <v>42.45916223526001</v>
+        <v>79.86115550994873</v>
       </c>
       <c r="D5" t="n">
-        <v>2.220000028610229</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1040699917536515</v>
+        <v>0.1057147236924674</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4236725568771362</v>
+        <v>0.5757570266723633</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4171542525291443</v>
+        <v>0.5664181709289551</v>
       </c>
       <c r="H5" t="n">
-        <v>0.384510338306427</v>
+        <v>0.503942608833313</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3749683499336242</v>
+        <v>0.4710245430469513</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0394613742828369</v>
+        <v>0.0411784648895263</v>
       </c>
       <c r="K5" t="n">
-        <v>18.01372599601746</v>
+        <v>12.39981603622436</v>
       </c>
       <c r="L5" t="n">
-        <v>1.076439142227173</v>
+        <v>1.068995714187622</v>
       </c>
       <c r="M5" t="n">
-        <v>3.017840623855591</v>
+        <v>2.997214317321777</v>
       </c>
       <c r="N5" t="n">
-        <v>4.959316730499268</v>
+        <v>4.690726518630981</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1794065237045288</v>
+        <v>0.1781659523646036</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5029734373092651</v>
+        <v>0.4995357195536296</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8265527884165446</v>
+        <v>0.7817877531051636</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250719-235704</t>
+          <t>20250723-095048</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5701,56 +5701,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>114</v>
+        <v>199</v>
       </c>
       <c r="C6" t="n">
-        <v>48.45416378974915</v>
+        <v>81.36177539825439</v>
       </c>
       <c r="D6" t="n">
         <v>2.319999933242798</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1053599788431535</v>
+        <v>0.1060528791130487</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4125459492206573</v>
+        <v>0.5833992958068848</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4051845073699951</v>
+        <v>0.5738546848297119</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3610811531543731</v>
+        <v>0.5183259844779968</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3651995062828064</v>
+        <v>0.5171107053756714</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0413248538970947</v>
+        <v>0.0436394214630126</v>
       </c>
       <c r="K6" t="n">
-        <v>18.30338549613953</v>
+        <v>17.87278056144714</v>
       </c>
       <c r="L6" t="n">
-        <v>1.107913970947266</v>
+        <v>1.097719192504883</v>
       </c>
       <c r="M6" t="n">
-        <v>3.061645984649658</v>
+        <v>3.284605741500854</v>
       </c>
       <c r="N6" t="n">
-        <v>4.710334300994873</v>
+        <v>4.908401012420654</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1846523284912109</v>
+        <v>0.1829531987508138</v>
       </c>
       <c r="P6" t="n">
-        <v>0.510274330774943</v>
+        <v>0.5474342902501425</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7850557168324789</v>
+        <v>0.8180668354034424</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250719-235905</t>
+          <t>20250723-095326</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
